--- a/data/trans_orig/P21D6_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>224799</t>
+          <t>228697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249562</t>
+          <t>250410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>262851</t>
+          <t>264384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279378</t>
+          <t>279617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>497247</t>
+          <t>496861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524128</t>
+          <t>524104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34885</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59942</t>
+          <t>60355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142120</t>
+          <t>159287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>604823</t>
+          <t>606811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>369378</t>
+          <t>368054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>394062</t>
+          <t>393707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>370764</t>
+          <t>392471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>979615</t>
+          <t>983965</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45261</t>
+          <t>43642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>511897</t>
+          <t>495755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37182</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>60629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98410</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>725412</t>
+          <t>698277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25095</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262887</t>
+          <t>263808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296938</t>
+          <t>295410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262851</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>286375</t>
+          <t>285809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534936</t>
+          <t>535391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>573790</t>
+          <t>574541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>18338</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>43881</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>73346</t>
+          <t>72626</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>27362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57242</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>330368</t>
+          <t>332693</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>363614</t>
+          <t>363591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>439352</t>
+          <t>439026</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>480736</t>
+          <t>480990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>780584</t>
+          <t>782301</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>835191</t>
+          <t>835299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36464</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66170</t>
+          <t>65646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61106</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72852</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120082</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>788091</t>
+          <t>748311</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1471616</t>
+          <t>1473332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1357003</t>
+          <t>1362623</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1416388</t>
+          <t>1420515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1952680</t>
+          <t>2021445</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2857998</t>
+          <t>2867653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>146098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>851847</t>
+          <t>899489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,82 +3134,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>148365</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>168345</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>524495</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>289109</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>1167496</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>148365</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>125826</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>172880</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>524495</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>294341</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1229180</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87328</t>
+          <t>88497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D6_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>240394</t>
+          <t>261397</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228697</t>
+          <t>246913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250410</t>
+          <t>270786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>272700</t>
+          <t>294709</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264384</t>
+          <t>285226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279617</t>
+          <t>301841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>513094</t>
+          <t>556106</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>496861</t>
+          <t>540894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>524104</t>
+          <t>569973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>35277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>25749</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31811</t>
+          <t>34757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>47713</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60355</t>
+          <t>61429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>684</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>375504</t>
+          <t>425741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159287</t>
+          <t>408385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>606811</t>
+          <t>440861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382230</t>
+          <t>430583</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>368054</t>
+          <t>413192</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>393707</t>
+          <t>443563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>757734</t>
+          <t>856324</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>392471</t>
+          <t>831946</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>983965</t>
+          <t>875591</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>277673</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43642</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>495755</t>
+          <t>57284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47684</t>
+          <t>53943</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>42694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>68018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>325357</t>
+          <t>92947</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>73720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>698277</t>
+          <t>117193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22218</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,67 +1668,67 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>6447</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>12280</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>2216</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>12834</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1104382</t>
+          <t>972007</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1104382</t>
+          <t>972007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1104382</t>
+          <t>972007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>282259</t>
+          <t>325299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263808</t>
+          <t>307538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295410</t>
+          <t>339334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>275408</t>
+          <t>320132</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261110</t>
+          <t>306710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285809</t>
+          <t>331578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>557667</t>
+          <t>645431</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535391</t>
+          <t>623113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574541</t>
+          <t>663569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>43457</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>60721</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43881</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>72626</t>
+          <t>77281</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>34278</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>42424</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>658632</t>
+          <t>753633</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>658632</t>
+          <t>753633</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>658632</t>
+          <t>753633</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>349867</t>
+          <t>374882</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>332693</t>
+          <t>359696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>363591</t>
+          <t>389253</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>456175</t>
+          <t>426521</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>439026</t>
+          <t>412820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>480990</t>
+          <t>438479</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>806043</t>
+          <t>801403</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>782301</t>
+          <t>779793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>835299</t>
+          <t>818241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>49571</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>65966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>49852</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29945</t>
+          <t>39835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63356</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>97316</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72783</t>
+          <t>83204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119159</t>
+          <t>121236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -2658,69 +2658,69 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>3079</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6918</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1248024</t>
+          <t>1387320</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>748311</t>
+          <t>1354637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1473332</t>
+          <t>1414435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1386513</t>
+          <t>1471945</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1362623</t>
+          <t>1446899</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1420515</t>
+          <t>1496572</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2634537</t>
+          <t>2859264</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2021445</t>
+          <t>2821703</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2867653</t>
+          <t>2897449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>376130</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146098</t>
+          <t>115632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>899489</t>
+          <t>171463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>148365</t>
+          <t>161669</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122343</t>
+          <t>143916</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168345</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>524495</t>
+          <t>300998</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>289109</t>
+          <t>267562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1167496</t>
+          <t>335956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48386</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>67086</t>
+          <t>71543</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88497</t>
+          <t>89490</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
